--- a/templates/import/monthly-goals.xlsx
+++ b/templates/import/monthly-goals.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="1" r:id="R9e9b7e5d1a764874"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="2" r:id="Rd0ce90597b124160"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="1" r:id="R88a8c3c5cde7420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="2" r:id="Raa26389009074d9b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,6 +14,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -145,7 +149,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -188,6 +192,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -523,8 +532,8 @@
       <x:c r="C5" s="11" t="str">
         <x:v>目标数值</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>演示数据</x:v>
+      <x:c r="D5" s="30" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
         <x:v>否</x:v>
@@ -571,16 +580,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="19" t="str">
-        <x:v>演示目标</x:v>
+        <x:v>匿名导入目标 A</x:v>
       </x:c>
       <x:c r="B2" s="20" t="str">
         <x:v>GMV</x:v>
       </x:c>
-      <x:c r="C2" s="20" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="D2" s="21" t="str">
-        <x:v>演示数据</x:v>
+      <x:c r="C2" s="28" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="D2" s="29" t="n">
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
